--- a/sources/ling_step4.xlsx
+++ b/sources/ling_step4.xlsx
@@ -423,8 +423,8 @@
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">

--- a/sources/ling_step4.xlsx
+++ b/sources/ling_step4.xlsx
@@ -852,6 +852,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -894,6 +899,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -936,6 +946,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -976,6 +991,11 @@
       <c r="L12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -7426,6 +7446,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -7451,6 +7476,11 @@
       <c r="J150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
